--- a/SCPI_DEF.xlsx
+++ b/SCPI_DEF.xlsx
@@ -1,32 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\achtenj\Desktop\Pyvisa-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joris\Documents\GitHub\Pyvisa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BA57B3-2D38-402F-A2A1-CA2EBD336314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F177EF1A-FEC7-415B-89D4-11367141854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5820" yWindow="375" windowWidth="19395" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="XDM2041" sheetId="1" r:id="rId1"/>
-    <sheet name="KA3005PS" sheetId="2" r:id="rId2"/>
-    <sheet name="KA3005P" sheetId="3" r:id="rId3"/>
-    <sheet name="GDM9061" sheetId="12" r:id="rId4"/>
-    <sheet name="SDG2042X" sheetId="9" r:id="rId5"/>
-    <sheet name="SDG1032X" sheetId="4" r:id="rId6"/>
-    <sheet name="Z650-1-U" sheetId="5" r:id="rId7"/>
-    <sheet name="SDS1104X-U" sheetId="6" r:id="rId8"/>
-    <sheet name="SDS1204X-E" sheetId="8" r:id="rId9"/>
-    <sheet name="SDS5034X" sheetId="10" r:id="rId10"/>
-    <sheet name="DS4024" sheetId="11" r:id="rId11"/>
-    <sheet name="SDL1020X-E" sheetId="7" r:id="rId12"/>
+    <sheet name="INDEX" sheetId="13" r:id="rId1"/>
+    <sheet name="XDM2041" sheetId="1" r:id="rId2"/>
+    <sheet name="GDM9061" sheetId="12" r:id="rId3"/>
+    <sheet name="KA3005PS" sheetId="2" r:id="rId4"/>
+    <sheet name="KA3005P" sheetId="3" r:id="rId5"/>
+    <sheet name="Z650-1-U" sheetId="5" r:id="rId6"/>
+    <sheet name="SDG2042X" sheetId="9" r:id="rId7"/>
+    <sheet name="SDG1032X" sheetId="4" r:id="rId8"/>
+    <sheet name="SDS1104X-U" sheetId="6" r:id="rId9"/>
+    <sheet name="SDS1204X-E" sheetId="8" r:id="rId10"/>
+    <sheet name="SDS5034X" sheetId="10" r:id="rId11"/>
+    <sheet name="DS4024" sheetId="11" r:id="rId12"/>
+    <sheet name="SDL1020X-E" sheetId="7" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">INDEX!$B$1:$F$12</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -79,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="341">
   <si>
     <t>Name</t>
   </si>
@@ -994,13 +1012,121 @@
   </si>
   <si>
     <t>READ?</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>DMM</t>
+  </si>
+  <si>
+    <t>5,5 digit digital multimeter</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>Korad</t>
+  </si>
+  <si>
+    <t>30V 5A lab power supply</t>
+  </si>
+  <si>
+    <t>DC power supply</t>
+  </si>
+  <si>
+    <t>Owon</t>
+  </si>
+  <si>
+    <t>REMARK</t>
+  </si>
+  <si>
+    <t>starting a measurment might require to read a few times before it's working</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>USB / LAN</t>
+  </si>
+  <si>
+    <t>6,5 digit digtal multimeter</t>
+  </si>
+  <si>
+    <t>Gwinstek</t>
+  </si>
+  <si>
+    <t>Function generator</t>
+  </si>
+  <si>
+    <t>40Mhz - 2 channel function generator</t>
+  </si>
+  <si>
+    <t>Sigilent</t>
+  </si>
+  <si>
+    <t>30Mhz - 2 channel function generator</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>DC power supply 650V</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>4 channel - 100Mhz 250MSa/s</t>
+  </si>
+  <si>
+    <t>4 channel - 200Mhz 500MSa/s</t>
+  </si>
+  <si>
+    <t>Oscilloscope</t>
+  </si>
+  <si>
+    <t>4 channel - 350Mhz 2,5GSa/s</t>
+  </si>
+  <si>
+    <t>Electrical load</t>
+  </si>
+  <si>
+    <t>150V / 30A 200W DC Load</t>
+  </si>
+  <si>
+    <t>Tested</t>
+  </si>
+  <si>
+    <t>4 channel - 200Mhz 4GSa/s</t>
+  </si>
+  <si>
+    <t>Rigol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1029,8 +1155,28 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1049,8 +1195,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1058,13 +1209,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1099,8 +1266,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Check Cell" xfId="3" builtinId="23"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{2F2D2794-8A0B-4E78-870A-48AC4486BC12}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2644,255 +2815,321 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAAF777-AA56-44FD-8C88-95464F27D83A}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="30.44140625" customWidth="1"/>
-    <col min="4" max="4" width="63.6640625" customWidth="1"/>
-    <col min="7" max="7" width="40.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" customWidth="1"/>
+    <col min="7" max="7" width="78.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>338</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>306</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>308</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>6</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A2" s="14" t="str">
+        <f>HYPERLINK("#'XDM2041'!A1", "XDM2041")</f>
+        <v>XDM2041</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>310</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>10</v>
+        <v>311</v>
+      </c>
+      <c r="D2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A3" s="14" t="str">
+        <f>HYPERLINK("#'KA3005PS'!A1", "KA3005PS")</f>
+        <v>KA3005PS</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>310</v>
+      </c>
+      <c r="C3" t="s">
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>14</v>
+        <v>314</v>
+      </c>
+      <c r="E3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A4" s="14" t="str">
+        <f>HYPERLINK("#'KA3005P'!A1", "KA3005P")</f>
+        <v>KA3005P</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>310</v>
+      </c>
+      <c r="C4" t="s">
+        <v>316</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>17</v>
+        <v>314</v>
+      </c>
+      <c r="E4" t="s">
+        <v>315</v>
+      </c>
+      <c r="F4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A5" s="14" t="str">
+        <f>HYPERLINK("#'GDM9061'!A1", "GDM9061")</f>
+        <v>GDM9061</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>310</v>
+      </c>
+      <c r="C5" t="s">
+        <v>311</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>323</v>
+      </c>
+      <c r="E5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A6" s="14" t="str">
+        <f>HYPERLINK("#'SDG2042X'!A1", "SDG2042X")</f>
+        <v>SDG2042X</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>324</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>326</v>
+      </c>
+      <c r="E6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A7" s="14" t="str">
+        <f>HYPERLINK("#'SDG1032X'!A1", "SDG1032X")</f>
+        <v>SDG1032X</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>310</v>
+      </c>
+      <c r="C7" t="s">
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>25</v>
+        <v>326</v>
+      </c>
+      <c r="E7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A8" s="14" t="str">
+        <f>HYPERLINK("#'Z650-1-U'!A1", "Z650-1-U")</f>
+        <v>Z650-1-U</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>328</v>
+      </c>
+      <c r="C8" t="s">
+        <v>316</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>27</v>
+        <v>330</v>
+      </c>
+      <c r="E8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A9" s="14" t="str">
+        <f>HYPERLINK("#'SDS1104X-U'!A1", "SDS1104X-U")</f>
+        <v>SDS1104X-U</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>331</v>
+      </c>
+      <c r="C9" t="s">
+        <v>334</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>30</v>
+        <v>326</v>
+      </c>
+      <c r="E9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A10" s="14" t="str">
+        <f>HYPERLINK("#'SDS1204X-E'!A1", "SDS1204X-E")</f>
+        <v>SDS1204X-E</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>32</v>
+        <v>331</v>
+      </c>
+      <c r="C10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A11" s="14" t="str">
+        <f>HYPERLINK("#'SDS5034X'!A1", "SDS5034X")</f>
+        <v>SDS5034X</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>34</v>
+        <v>331</v>
+      </c>
+      <c r="C11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A12" s="14" t="str">
+        <f>HYPERLINK("#'SDL1020X-E'!A1", "SDL1020X-E")</f>
+        <v>SDL1020X-E</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>36</v>
+        <v>328</v>
+      </c>
+      <c r="C12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="A13" s="14" t="str">
+        <f>HYPERLINK("#'DS4024'!A1", "DS4024")</f>
+        <v>DS4024</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="4">
-        <v>-96.000169999999997</v>
-      </c>
-    </row>
+        <v>331</v>
+      </c>
+      <c r="C13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>339</v>
+      </c>
+      <c r="F13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickTop="1"/>
   </sheetData>
+  <autoFilter ref="B1:F12" xr:uid="{4FAAF777-AA56-44FD-8C88-95464F27D83A}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97FABA3-097E-44FB-AC44-DC43E2BCB82B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C850955B-3547-4061-AAB8-09C8A9620129}">
   <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
+    <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="162.44140625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="162.42578125" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3282,15 +3519,18 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0007AE-3B2E-4FE7-ACEA-9693B81B394D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97FABA3-097E-44FB-AC44-DC43E2BCB82B}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="162.44140625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="162.42578125" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3312,6 +3552,407 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A13" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0007AE-3B2E-4FE7-ACEA-9693B81B394D}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="162.42578125" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="8" t="s">
         <v>105</v>
       </c>
@@ -3492,7 +4133,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="43.2">
+    <row r="16" spans="1:5" ht="45">
       <c r="A16" s="8" t="s">
         <v>180</v>
       </c>
@@ -3603,7 +4244,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="43.2">
+    <row r="28" spans="1:6" ht="60">
       <c r="A28" s="8" t="s">
         <v>203</v>
       </c>
@@ -3662,15 +4303,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7811CF-7B67-4481-8807-C8AB2B6C2465}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3784,18 +4428,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="63.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -3811,75 +4454,212 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>171</v>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>175</v>
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>176</v>
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>177</v>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="4">
+        <v>-96.000169999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3888,121 +4668,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD2A42B-4009-4001-8094-279CF8DAC6AE}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
-    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD2A42B-4009-4001-8094-279CF8DAC6AE}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4139,19 +4815,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2515B59-885B-40AA-A8E1-AF69E35D6498}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor theme="7" tint="0.39997558519241921"/>
+    <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="82.33203125" customWidth="1"/>
-    <col min="7" max="7" width="85.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -4167,425 +4843,95 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="6"/>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
-      <c r="G3" s="6"/>
+      <c r="A3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="G4" s="6"/>
+      <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="G5" s="6"/>
+      <c r="A5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="5"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="5"/>
-      <c r="G27" s="6"/>
+      <c r="A6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor theme="7" tint="0.39997558519241921"/>
+    <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="82.33203125" customWidth="1"/>
-    <col min="7" max="7" width="85.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -4604,463 +4950,94 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="6"/>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
-      <c r="G3" s="6"/>
+      <c r="A3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="G4" s="6"/>
+      <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="G5" s="6"/>
+      <c r="A5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A16" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="5"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="5"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="5"/>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="5"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="5"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="5"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="5"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" spans="1:7" ht="27.9" customHeight="1">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="5"/>
-      <c r="G33" s="6"/>
+      <c r="A6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D8A7FA-2F93-4DD6-BBE2-8941E214B32F}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.109375" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5319,19 +5296,932 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2515B59-885B-40AA-A8E1-AF69E35D6498}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82.28515625" customWidth="1"/>
+    <col min="7" max="7" width="85.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="12"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="5"/>
+      <c r="G27" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82.28515625" customWidth="1"/>
+    <col min="7" max="7" width="85.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="12"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A20" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="5"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="5"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="5"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="5"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="5"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="5"/>
+      <c r="G33" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC2B197-BBF6-4032-B079-82991FDC08F6}">
   <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
+    <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="162.44140625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="162.42578125" customWidth="1"/>
+    <col min="5" max="5" width="46.7109375" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5714,412 +6604,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="33" customFormat="1"/>
-    <row r="34" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C850955B-3547-4061-AAB8-09C8A9620129}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="37.44140625" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="162.44140625" customWidth="1"/>
-    <col min="5" max="5" width="46.6640625" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="D25" s="8"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>